--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER RAKE_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER RAKE_CS.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.201</v>
+        <v>0.3138</v>
       </c>
       <c r="H4" t="n">
         <v>0.2402</v>
@@ -542,10 +542,10 @@
         <v>0.2473</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2125</v>
+        <v>0.2676</v>
       </c>
       <c r="H5" t="n">
-        <v>0.202</v>
+        <v>0.2574</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.3452</v>
+        <v>0.3909</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2391</v>
+        <v>0.3354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2135</v>
+        <v>0.3524</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -648,7 +648,7 @@
         <v>0.2876</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3001</v>
+        <v>0.324</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -718,7 +718,7 @@
         <v>0.3081</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2821</v>
+        <v>0.2899</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -784,22 +784,22 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2116</v>
+        <v>0.4136</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2126</v>
+        <v>0.3109</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2958</v>
+        <v>0.3408</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2969</v>
+        <v>0.4187</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2097</v>
+        <v>0.2621</v>
       </c>
       <c r="H19" t="n">
-        <v>0.333</v>
+        <v>0.3859</v>
       </c>
     </row>
     <row r="20">
@@ -810,7 +810,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.2219</v>
+        <v>0.2259</v>
       </c>
       <c r="D20" t="n">
         <v>0.2255</v>
@@ -823,7 +823,7 @@
         <v>0.2244</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2416</v>
+        <v>0.2484</v>
       </c>
     </row>
     <row r="21">
@@ -861,7 +861,7 @@
         <v>0.2489</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2057</v>
+        <v>0.2377</v>
       </c>
       <c r="G22" t="n">
         <v>0.208</v>
@@ -894,7 +894,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.245</v>
+        <v>0.2487</v>
       </c>
       <c r="H24" t="n">
         <v>0.2299</v>
@@ -960,7 +960,7 @@
         <v>0.2878</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2807</v>
+        <v>0.2848</v>
       </c>
       <c r="H27" t="n">
         <v>0.2752</v>
@@ -1084,16 +1084,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.2339</v>
+        <v>0.3729</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2253</v>
+        <v>0.3735</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2193</v>
+        <v>0.287</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2049</v>
+        <v>0.3646</v>
       </c>
     </row>
     <row r="36">
@@ -1104,19 +1104,19 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.2895</v>
+        <v>0.3572</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3118</v>
+        <v>0.4197</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3035</v>
+        <v>0.4187</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2947</v>
+        <v>0.3492</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2582</v>
+        <v>0.3076</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>0.2109</v>
+        <v>0.229</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1205,13 +1205,13 @@
         <v>0.2471</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2164</v>
+        <v>0.2831</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2217</v>
+        <v>0.3169</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2594</v>
+        <v>0.2763</v>
       </c>
       <c r="G42" t="n">
         <v>0.3087</v>
@@ -1226,22 +1226,22 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.2276</v>
+        <v>0.266</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2127</v>
+        <v>0.2479</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2479</v>
+        <v>0.2498</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2009</v>
+        <v>0.2792</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2454</v>
+        <v>0.2473</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2194</v>
+        <v>0.3191</v>
       </c>
     </row>
     <row r="44">
@@ -1288,7 +1288,7 @@
         <v>0.2472</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2311</v>
+        <v>0.2358</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1302,14 +1302,14 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.2041</v>
+        <v>0.2366</v>
       </c>
       <c r="D47" t="n">
         <v>0.2038</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>0.2026</v>
+        <v>0.2424</v>
       </c>
       <c r="G47" t="n">
         <v>0.2529</v>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.2035</v>
+        <v>0.2994</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>0.2368</v>
+        <v>0.3798</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2059</v>
+        <v>0.3047</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2145</v>
+        <v>0.3447</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1362,14 +1362,14 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>0.2085</v>
+        <v>0.2255</v>
       </c>
       <c r="F50" t="n">
         <v>0.2063</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0.2028</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2057</v>
+        <v>0.279</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2021</v>
+        <v>0.2561</v>
       </c>
       <c r="E52" t="n">
-        <v>0.247</v>
+        <v>0.3364</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2142</v>
+        <v>0.275</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2121</v>
+        <v>0.2688</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1422,16 +1422,16 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.2092</v>
+        <v>0.2786</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2104</v>
+        <v>0.2185</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2245</v>
+        <v>0.2364</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2435</v>
+        <v>0.2578</v>
       </c>
       <c r="G53" t="n">
         <v>0.2333</v>
@@ -1446,19 +1446,19 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.245</v>
+        <v>0.3709</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2022</v>
+        <v>0.2773</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2397</v>
+        <v>0.3476</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2386</v>
+        <v>0.3064</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2323</v>
+        <v>0.3449</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1470,19 +1470,19 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2132</v>
+        <v>0.2459</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2526</v>
+        <v>0.317</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2328</v>
+        <v>0.3282</v>
       </c>
       <c r="F55" t="n">
         <v>0.2619</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2175</v>
+        <v>0.2648</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1497,7 +1497,7 @@
         <v>0.2521</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2006</v>
+        <v>0.2201</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
@@ -1516,19 +1516,19 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0.219</v>
+        <v>0.2455</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2098</v>
+        <v>0.2838</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2549</v>
+        <v>0.3162</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2539</v>
+        <v>0.332</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2209</v>
+        <v>0.221</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0.2214</v>
+        <v>0.307</v>
       </c>
       <c r="D58" t="n">
         <v>0.2479</v>
@@ -1563,22 +1563,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2543</v>
+        <v>0.4087</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2624</v>
+        <v>0.4581</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2601</v>
+        <v>0.424</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2145</v>
+        <v>0.3605</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2281</v>
+        <v>0.2839</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2011</v>
+        <v>0.2578</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.29</v>
+        <v>0.3735</v>
       </c>
       <c r="C60" t="n">
-        <v>0.3229</v>
+        <v>0.5992</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2495</v>
+        <v>0.4867</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2654</v>
+        <v>0.4437</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2174</v>
+        <v>0.2322</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2326</v>
+        <v>0.2822</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1615,22 +1615,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2171</v>
+        <v>0.3345</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3018</v>
+        <v>0.5235</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2709</v>
+        <v>0.4554</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2124</v>
+        <v>0.3504</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2083</v>
+        <v>0.2717</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2082</v>
+        <v>0.2349</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2101</v>
+        <v>0.2137</v>
       </c>
       <c r="D62" t="n">
         <v>0.2093</v>
@@ -1651,10 +1651,10 @@
         <v>0.2322</v>
       </c>
       <c r="F62" t="n">
-        <v>0.233</v>
+        <v>0.2405</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2086</v>
+        <v>0.2093</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1726,13 +1726,13 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0.2071</v>
+        <v>0.2873</v>
       </c>
       <c r="D67" t="n">
         <v>0.3056</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2265</v>
+        <v>0.3345</v>
       </c>
       <c r="F67" t="n">
         <v>0.2293</v>
@@ -1750,19 +1750,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2252</v>
+        <v>0.3113</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2495</v>
+        <v>0.3673</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2768</v>
+        <v>0.4208</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3013</v>
+        <v>0.4513</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2551</v>
+        <v>0.3721</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1774,16 +1774,16 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.2627</v>
+        <v>0.3996</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3058</v>
+        <v>0.455</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2985</v>
+        <v>0.4348</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2793</v>
+        <v>0.435</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -1799,13 +1799,13 @@
         <v>0.2619</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2415</v>
+        <v>0.3006</v>
       </c>
       <c r="E70" t="n">
-        <v>0.228</v>
+        <v>0.2964</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2064</v>
+        <v>0.3286</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -1821,19 +1821,19 @@
         <v>0.2582</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2051</v>
+        <v>0.3378</v>
       </c>
       <c r="E71" t="n">
-        <v>0.21</v>
+        <v>0.3675</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2855</v>
+        <v>0.3131</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2229</v>
+        <v>0.3069</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2327</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="72">
@@ -1847,13 +1847,13 @@
         <v>0.3303</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2308</v>
+        <v>0.3625</v>
       </c>
       <c r="E72" t="n">
         <v>0.3171</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2201</v>
+        <v>0.3422</v>
       </c>
       <c r="G72" t="n">
         <v>0.2971</v>
@@ -1868,19 +1868,19 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.2365</v>
+        <v>0.4013</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2373</v>
+        <v>0.4104</v>
       </c>
       <c r="E73" t="n">
         <v>0.3392</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2833</v>
+        <v>0.4203</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2586</v>
+        <v>0.2679</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -1910,19 +1910,19 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.3239</v>
+        <v>0.4926</v>
       </c>
       <c r="D75" t="n">
-        <v>0.371</v>
+        <v>0.5903</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3995</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3099</v>
+        <v>0.4647</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3093</v>
+        <v>0.4742</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -1934,13 +1934,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.2008</v>
+        <v>0.2893</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2099</v>
+        <v>0.2529</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2032</v>
+        <v>0.2348</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -1954,16 +1954,16 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.2165</v>
+        <v>0.3197</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2189</v>
+        <v>0.3201</v>
       </c>
       <c r="E77" t="n">
         <v>0.3217</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2001</v>
+        <v>0.3324</v>
       </c>
       <c r="G77" t="n">
         <v>0.2632</v>
@@ -1987,10 +1987,10 @@
         <v>0.2805</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2307</v>
+        <v>0.3435</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2205</v>
+        <v>0.2845</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2016,16 +2016,16 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.2224</v>
+        <v>0.2407</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2332</v>
+        <v>0.2445</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2017</v>
+        <v>0.2098</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2222</v>
+        <v>0.2268</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2038,19 +2038,19 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2461</v>
+        <v>0.2711</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2556</v>
+        <v>0.4307</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2414</v>
+        <v>0.4021</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2164</v>
+        <v>0.3465</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2347</v>
+        <v>0.3292</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2065,7 +2065,7 @@
         <v>0.2034</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2016</v>
+        <v>0.2149</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
@@ -2117,11 +2117,11 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>0.2176</v>
+        <v>0.2377</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>0.2017</v>
+        <v>0.2087</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
         <v>0.3448</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2133</v>
+        <v>0.4016</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2046</v>
+        <v>0.4057</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2596</v>
+        <v>0.4612</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2929</v>
+        <v>0.404</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2192,7 +2192,7 @@
         <v>0.2153</v>
       </c>
       <c r="G89" t="n">
-        <v>0.2168</v>
+        <v>0.2403</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2207,7 +2207,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.2028</v>
+        <v>0.207</v>
       </c>
       <c r="G90" t="n">
         <v>0.2088</v>
@@ -2222,16 +2222,16 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.2054</v>
+        <v>0.2107</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2013</v>
+        <v>0.2302</v>
       </c>
       <c r="E91" t="n">
         <v>0.2654</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2043</v>
+        <v>0.2314</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2243,19 +2243,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2457</v>
+        <v>0.3362</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2452</v>
+        <v>0.2836</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2882</v>
+        <v>0.3274</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2969</v>
+        <v>0.3812</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2512</v>
+        <v>0.3439</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -2268,16 +2268,16 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.2077</v>
+        <v>0.3212</v>
       </c>
       <c r="D93" t="n">
         <v>0.2121</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2132</v>
+        <v>0.2736</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2183</v>
+        <v>0.2317</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2348</v>
+        <v>0.4348</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2096</v>
+        <v>0.3352</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2152</v>
+        <v>0.4056</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2088</v>
+        <v>0.4004</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2064</v>
+        <v>0.401</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2380,19 +2380,19 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.3974</v>
+        <v>0.4163</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3333</v>
+        <v>0.3499</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2134</v>
+        <v>0.2429</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3571</v>
+        <v>0.3757</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2793</v>
+        <v>0.377</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2424,19 +2424,19 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2169</v>
+        <v>0.298</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2045</v>
+        <v>0.2943</v>
       </c>
       <c r="E101" t="n">
-        <v>0.206</v>
+        <v>0.3053</v>
       </c>
       <c r="F101" t="n">
-        <v>0.207</v>
+        <v>0.2737</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2511</v>
+        <v>0.2556</v>
       </c>
       <c r="H101" t="n">
         <v>0.2356</v>
@@ -2465,13 +2465,13 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>0.2384</v>
+        <v>0.2689</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2162</v>
+        <v>0.2233</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2156</v>
+        <v>0.2685</v>
       </c>
       <c r="G103" t="n">
         <v>0.223</v>
@@ -2527,7 +2527,7 @@
         <v>0.2231</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2033</v>
+        <v>0.2531</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
@@ -2554,13 +2554,13 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.2056</v>
+        <v>0.2236</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2091</v>
+        <v>0.2752</v>
       </c>
       <c r="E108" t="n">
-        <v>0.214</v>
+        <v>0.2535</v>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
@@ -2618,19 +2618,19 @@
         <v>0.2597</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2439</v>
+        <v>0.2944</v>
       </c>
       <c r="D111" t="n">
-        <v>0.209</v>
+        <v>0.2399</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2144</v>
+        <v>0.2611</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2632</v>
+        <v>0.3654</v>
       </c>
       <c r="G111" t="n">
-        <v>0.2112</v>
+        <v>0.284</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -2664,16 +2664,16 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0.2035</v>
+        <v>0.2972</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2133</v>
+        <v>0.2598</v>
       </c>
       <c r="E113" t="n">
-        <v>0.219</v>
+        <v>0.2597</v>
       </c>
       <c r="F113" t="n">
-        <v>0.219</v>
+        <v>0.3113</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -2738,19 +2738,19 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>0.2026</v>
+        <v>0.4487</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2023</v>
+        <v>0.3461</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2334</v>
+        <v>0.3263</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2149</v>
+        <v>0.3533</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2403</v>
+        <v>0.3099</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -2796,10 +2796,10 @@
         <v>0.2922</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3817</v>
+        <v>0.4032</v>
       </c>
       <c r="F120" t="n">
-        <v>0.414</v>
+        <v>0.4157</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
         <v>0.2367</v>
       </c>
       <c r="D136" t="n">
-        <v>0.2099</v>
+        <v>0.2906</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
@@ -3075,16 +3075,16 @@
         <v>0.3911</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2162</v>
+        <v>0.2964</v>
       </c>
       <c r="E138" t="n">
-        <v>0.2427</v>
+        <v>0.3966</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2025</v>
+        <v>0.3597</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2382</v>
+        <v>0.2916</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3129,16 +3129,16 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.2039</v>
+        <v>0.3677</v>
       </c>
       <c r="E141" t="n">
         <v>0.2375</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2136</v>
+        <v>0.359</v>
       </c>
       <c r="G141" t="n">
-        <v>0.2028</v>
+        <v>0.2911</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3149,22 +3149,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2085</v>
+        <v>0.3945</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2304</v>
+        <v>0.3257</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2088</v>
+        <v>0.372</v>
       </c>
       <c r="E142" t="n">
         <v>0.3605</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2045</v>
+        <v>0.3899</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2002</v>
+        <v>0.3423</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3178,16 +3178,16 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.2346</v>
+        <v>0.4945</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2298</v>
+        <v>0.4842</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2229</v>
+        <v>0.4689</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2466</v>
+        <v>0.4634</v>
       </c>
     </row>
     <row r="144">
@@ -3199,7 +3199,7 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.2022</v>
+        <v>0.4485</v>
       </c>
       <c r="E144" t="n">
         <v>0.4365</v>
@@ -3225,7 +3225,7 @@
         <v>0.2549</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2019</v>
+        <v>0.2727</v>
       </c>
       <c r="G145" t="n">
         <v>0.2405</v>
@@ -3261,13 +3261,13 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="n">
-        <v>0.259</v>
+        <v>0.4789</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2155</v>
+        <v>0.4182</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2103</v>
+        <v>0.357</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
@@ -3280,16 +3280,16 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0.254</v>
+        <v>0.3349</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2486</v>
+        <v>0.3966</v>
       </c>
       <c r="E148" t="n">
-        <v>0.27</v>
+        <v>0.4212</v>
       </c>
       <c r="F148" t="n">
-        <v>0.2399</v>
+        <v>0.339</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
